--- a/SPLIT_COMPANY_DATA/RESULT/companies_result/КСУДС/КСУДС.xlsx
+++ b/SPLIT_COMPANY_DATA/RESULT/companies_result/КСУДС/КСУДС.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="51" uniqueCount="30">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="40" uniqueCount="24">
   <si>
     <t>Дата</t>
   </si>
@@ -34,9 +34,6 @@
     <t>Литри</t>
   </si>
   <si>
-    <t>Тип количество</t>
-  </si>
-  <si>
     <t>GTA цена</t>
   </si>
   <si>
@@ -58,10 +55,7 @@
     <t>Billing_Document</t>
   </si>
   <si>
-    <t>1148 Варна пристанище</t>
-  </si>
-  <si>
-    <t>1158 Варна Чайка</t>
+    <t>Варна Чайка</t>
   </si>
   <si>
     <t>В5689ВН</t>
@@ -73,19 +67,7 @@
     <t>DIESEL EKONOMY</t>
   </si>
   <si>
-    <t>L15</t>
-  </si>
-  <si>
-    <t>13:53:00</t>
-  </si>
-  <si>
-    <t>11:22:00</t>
-  </si>
-  <si>
-    <t>3236520848 3236520848</t>
-  </si>
-  <si>
-    <t>3237062867 3237062867</t>
+    <t>11:20</t>
   </si>
   <si>
     <t>Общи литри по продукт / КСУДС</t>
@@ -508,7 +490,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:N9"/>
+  <dimension ref="A1:M8"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="35.7109375" customWidth="1"/>
@@ -517,17 +499,16 @@
     <col min="4" max="4" width="28.7109375" customWidth="1"/>
     <col min="5" max="5" width="22.7109375" customWidth="1"/>
     <col min="6" max="6" width="18.7109375" customWidth="1"/>
-    <col min="7" max="7" width="16.7109375" customWidth="1"/>
+    <col min="7" max="7" width="15.7109375" style="1" customWidth="1"/>
     <col min="8" max="8" width="23.7109375" customWidth="1"/>
     <col min="9" max="9" width="15.7109375" style="1" customWidth="1"/>
     <col min="10" max="10" width="23.7109375" customWidth="1"/>
-    <col min="11" max="11" width="15.7109375" style="1" customWidth="1"/>
-    <col min="12" max="12" width="10.7109375" customWidth="1"/>
-    <col min="13" max="13" width="11.7109375" customWidth="1"/>
-    <col min="14" max="14" width="23.7109375" customWidth="1"/>
+    <col min="11" max="11" width="7.7109375" customWidth="1"/>
+    <col min="12" max="12" width="11.7109375" customWidth="1"/>
+    <col min="13" max="13" width="18.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:14">
+    <row r="1" spans="1:13">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
@@ -567,169 +548,119 @@
       <c r="M1" s="2" t="s">
         <v>12</v>
       </c>
-      <c r="N1" s="2" t="s">
+    </row>
+    <row r="2" spans="1:13">
+      <c r="A2" s="3">
+        <v>46279</v>
+      </c>
+      <c r="B2" t="s">
         <v>13</v>
       </c>
+      <c r="C2" t="s">
+        <v>14</v>
+      </c>
+      <c r="D2" t="s">
+        <v>15</v>
+      </c>
+      <c r="E2" t="s">
+        <v>16</v>
+      </c>
+      <c r="F2">
+        <v>48.48</v>
+      </c>
+      <c r="G2" s="1">
+        <v>1.89</v>
+      </c>
+      <c r="H2" s="1">
+        <v>91.627</v>
+      </c>
+      <c r="I2" s="1">
+        <v>1.92</v>
+      </c>
+      <c r="J2" s="1">
+        <v>93.08199999999999</v>
+      </c>
+      <c r="K2" t="s">
+        <v>17</v>
+      </c>
+      <c r="L2">
+        <v>71367</v>
+      </c>
+      <c r="M2">
+        <v>5418</v>
+      </c>
     </row>
-    <row r="2" spans="1:14">
-      <c r="A2" s="3">
-        <v>46251</v>
-      </c>
-      <c r="B2" t="s">
-        <v>14</v>
-      </c>
-      <c r="C2" t="s">
+    <row r="5" spans="1:13">
+      <c r="A5" s="4" t="s">
+        <v>18</v>
+      </c>
+      <c r="B5" s="4"/>
+      <c r="C5" s="4"/>
+      <c r="D5" s="4"/>
+      <c r="E5" s="4"/>
+      <c r="F5" s="4"/>
+    </row>
+    <row r="6" spans="1:13">
+      <c r="A6" s="5" t="s">
+        <v>19</v>
+      </c>
+      <c r="B6" s="5" t="s">
+        <v>20</v>
+      </c>
+      <c r="C6" s="5" t="s">
+        <v>21</v>
+      </c>
+      <c r="D6" s="5" t="s">
+        <v>22</v>
+      </c>
+      <c r="E6" s="5" t="s">
+        <v>7</v>
+      </c>
+      <c r="F6" s="5" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="7" spans="1:13">
+      <c r="A7" s="6" t="s">
         <v>16</v>
       </c>
-      <c r="D2" t="s">
-        <v>17</v>
-      </c>
-      <c r="E2" t="s">
-        <v>18</v>
-      </c>
-      <c r="F2">
-        <v>47.05</v>
-      </c>
-      <c r="G2" t="s">
-        <v>19</v>
-      </c>
-      <c r="H2" s="1">
-        <v>1.77</v>
-      </c>
-      <c r="I2" s="1">
-        <v>83.27800000000001</v>
-      </c>
-      <c r="J2" s="1">
-        <v>1.8</v>
-      </c>
-      <c r="K2" s="1">
-        <v>84.69</v>
-      </c>
-      <c r="L2" t="s">
-        <v>20</v>
-      </c>
-      <c r="M2">
-        <v>70285</v>
-      </c>
-      <c r="N2" t="s">
-        <v>22</v>
+      <c r="B7" s="7">
+        <v>48.48</v>
+      </c>
+      <c r="C7" s="8">
+        <v>1</v>
+      </c>
+      <c r="D7" s="9">
+        <v>1.89</v>
+      </c>
+      <c r="E7" s="7">
+        <v>91.63</v>
+      </c>
+      <c r="F7" s="7">
+        <v>93.08</v>
       </c>
     </row>
-    <row r="3" spans="1:14">
-      <c r="A3" s="3">
-        <v>46262</v>
-      </c>
-      <c r="B3" t="s">
-        <v>15</v>
-      </c>
-      <c r="C3" t="s">
-        <v>16</v>
-      </c>
-      <c r="D3" t="s">
-        <v>17</v>
-      </c>
-      <c r="E3" t="s">
-        <v>18</v>
-      </c>
-      <c r="F3">
-        <v>51.64</v>
-      </c>
-      <c r="G3" t="s">
-        <v>19</v>
-      </c>
-      <c r="H3" s="1">
-        <v>1.82</v>
-      </c>
-      <c r="I3" s="1">
-        <v>93.985</v>
-      </c>
-      <c r="J3" s="1">
-        <v>1.85</v>
-      </c>
-      <c r="K3" s="1">
-        <v>95.53400000000001</v>
-      </c>
-      <c r="L3" t="s">
-        <v>21</v>
-      </c>
-      <c r="M3">
-        <v>70782</v>
-      </c>
-      <c r="N3" t="s">
+    <row r="8" spans="1:13">
+      <c r="A8" s="10" t="s">
         <v>23</v>
       </c>
-    </row>
-    <row r="6" spans="1:14">
-      <c r="A6" s="4" t="s">
-        <v>24</v>
-      </c>
-      <c r="B6" s="4"/>
-      <c r="C6" s="4"/>
-      <c r="D6" s="4"/>
-      <c r="E6" s="4"/>
-      <c r="F6" s="4"/>
-    </row>
-    <row r="7" spans="1:14">
-      <c r="A7" s="5" t="s">
-        <v>25</v>
-      </c>
-      <c r="B7" s="5" t="s">
-        <v>26</v>
-      </c>
-      <c r="C7" s="5" t="s">
-        <v>27</v>
-      </c>
-      <c r="D7" s="5" t="s">
-        <v>28</v>
-      </c>
-      <c r="E7" s="5" t="s">
-        <v>8</v>
-      </c>
-      <c r="F7" s="5" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="8" spans="1:14">
-      <c r="A8" s="6" t="s">
-        <v>18</v>
-      </c>
-      <c r="B8" s="7">
-        <v>98.69</v>
-      </c>
-      <c r="C8" s="8">
-        <v>2</v>
-      </c>
-      <c r="D8" s="9">
-        <v>1.79616</v>
-      </c>
-      <c r="E8" s="7">
-        <v>177.26</v>
-      </c>
-      <c r="F8" s="7">
-        <v>180.22</v>
-      </c>
-    </row>
-    <row r="9" spans="1:14">
-      <c r="A9" s="10" t="s">
-        <v>29</v>
-      </c>
-      <c r="B9" s="11">
-        <v>98.69</v>
-      </c>
-      <c r="C9" s="12">
-        <v>2</v>
-      </c>
-      <c r="D9" s="9"/>
-      <c r="E9" s="11">
-        <v>177.26</v>
-      </c>
-      <c r="F9" s="11">
-        <v>180.22</v>
+      <c r="B8" s="11">
+        <v>48.48</v>
+      </c>
+      <c r="C8" s="12">
+        <v>1</v>
+      </c>
+      <c r="D8" s="9"/>
+      <c r="E8" s="11">
+        <v>91.63</v>
+      </c>
+      <c r="F8" s="11">
+        <v>93.08</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="1">
-    <mergeCell ref="A6:F6"/>
+    <mergeCell ref="A5:F5"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
